--- a/region/Central-overview-grid.xlsx
+++ b/region/Central-overview-grid.xlsx
@@ -112,7 +112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:AD34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — Central — generated 8/18/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — Central — generated 9/15/2026</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Outdoor QD01 — ATX.SP104 Palm Way wallscape (The Domain, Austin), 10/19/26–1/3/27 — ✅ EXECUTED 8/7/26 (Sowrey 8/4 + Rappaport 8/7)</t>
+          <t xml:space="preserve">Big Outdoor QD01 — EXECUTED — ATX.SP104 Palm Way at Nordstrom (Austin wallscape)</t>
         </is>
       </c>
       <c r="R6" s="6">
@@ -595,7 +595,7 @@
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Outdoor QD01 ATX.SP104 EXECUTED 8-7-26 (both signed).pdf</t>
+          <t xml:space="preserve">Big Outdoor QD01 (ATX.SP104 Palm Way).pdf</t>
         </is>
       </c>
       <c r="U6" s="4">
@@ -700,22 +700,22 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267</t>
+          <t xml:space="preserve">E199</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Advertising</t>
+          <t xml:space="preserve">Gunnarson Outdoor Advertising</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brendolyn O'Connor</t>
+          <t xml:space="preserve">Jason Cragg</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boconnor@lamar.com</t>
+          <t xml:space="preserve">billboards@gunnarsonadvertising.com</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -730,78 +730,74 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">154946</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S MANCHACA 1000' N/O SLAUGHTER</t>
+          <t xml:space="preserve">IH-35, 1/4 mile south of Posey Road, MP 198.8 (E199RH — faces South, right-hand read)</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin</t>
+          <t xml:space="preserve">San Marcos</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78748</t>
+          <t xml:space="preserve">78666</t>
         </is>
       </c>
       <c r="K8" s="10">
-        <v>30.17579</v>
+        <v>29.813016</v>
       </c>
       <c r="L8" s="10">
-        <v>-97.82311</v>
+        <v>-98.000831</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">RH</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' 0" x 36' 0"</t>
+          <t xml:space="preserve">8' x 60'</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="6">
-        <v>46251</v>
+        <v>46296</v>
       </c>
       <c r="S8" s="6">
-        <v>46327</v>
+        <v>46660</v>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar C5659754 ATX 8-panel HEB-SIGNED 8-4-26 (awaiting Lamar GM).pdf</t>
+          <t xml:space="preserve">Gunnarson E199RH Lease HEB-SIGNED 9-11-26 (awaiting Gunnarson).pdf</t>
         </is>
       </c>
       <c r="U8" s="4">
-        <v>197174</v>
+        <v>381000</v>
       </c>
       <c r="V8" s="8">
-        <v>3150</v>
+        <v>1500</v>
       </c>
       <c r="W8" s="8"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="Z8" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="6"/>
@@ -810,7 +806,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305</t>
+          <t xml:space="preserve">1267</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -840,12 +836,12 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">154984</t>
+          <t xml:space="preserve">154946</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S US 183 N. 0.33 MI N/O RR 620</t>
+          <t xml:space="preserve">W/S MANCHACA 1000' N/O SLAUGHTER</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -855,14 +851,14 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78717</t>
+          <t xml:space="preserve">78748</t>
         </is>
       </c>
       <c r="K9" s="11">
-        <v>30.47592</v>
+        <v>30.17579</v>
       </c>
       <c r="L9" s="11">
-        <v>-97.79913</v>
+        <v>-97.82311</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
@@ -871,12 +867,12 @@
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' 0" x 48' 0"</t>
+          <t xml:space="preserve">12' 0" x 36' 0"</t>
         </is>
       </c>
       <c r="P9" s="5" t="inlineStr">
@@ -897,15 +893,15 @@
         </is>
       </c>
       <c r="U9" s="5">
-        <v>230021</v>
+        <v>197174</v>
       </c>
       <c r="V9" s="9">
-        <v>4050</v>
+        <v>3150</v>
       </c>
       <c r="W9" s="9"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" s="13" t="inlineStr">
         <is>
@@ -920,7 +916,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1377</t>
+          <t xml:space="preserve">1305</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -950,12 +946,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">155054</t>
+          <t xml:space="preserve">154984</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">US 290 2.25 MI W/O HWY 71</t>
+          <t xml:space="preserve">E/S US 183 N. 0.33 MI N/O RR 620</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -965,18 +961,18 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78736</t>
+          <t xml:space="preserve">78717</t>
         </is>
       </c>
       <c r="K10" s="10">
-        <v>30.23466692</v>
+        <v>30.47592</v>
       </c>
       <c r="L10" s="10">
-        <v>-97.91251804</v>
+        <v>-97.79913</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -986,7 +982,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' 0" x 36' 0"</t>
+          <t xml:space="preserve">14' 0" x 48' 0"</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -1007,15 +1003,15 @@
         </is>
       </c>
       <c r="U10" s="4">
-        <v>160519</v>
+        <v>230021</v>
       </c>
       <c r="V10" s="8">
-        <v>2250</v>
+        <v>4050</v>
       </c>
       <c r="W10" s="8"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="Z10" s="12" t="inlineStr">
         <is>
@@ -1030,7 +1026,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1503</t>
+          <t xml:space="preserve">1377</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1055,48 +1051,48 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">155166</t>
+          <t xml:space="preserve">155054</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35 @ MM 265.2 IN GEORGETOWN</t>
+          <t xml:space="preserve">US 290 2.25 MI W/O HWY 71</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georgetown</t>
+          <t xml:space="preserve">Austin</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78628</t>
+          <t xml:space="preserve">78736</t>
         </is>
       </c>
       <c r="K11" s="11">
-        <v>30.683</v>
+        <v>30.23466692</v>
       </c>
       <c r="L11" s="11">
-        <v>-97.6604</v>
+        <v>-97.91251804</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">12' 0" x 36' 0"</t>
         </is>
       </c>
       <c r="P11" s="5" t="inlineStr">
@@ -1117,15 +1113,15 @@
         </is>
       </c>
       <c r="U11" s="5">
-        <v>407496</v>
+        <v>160519</v>
       </c>
       <c r="V11" s="9">
-        <v>4050</v>
+        <v>2250</v>
       </c>
       <c r="W11" s="9"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" s="13" t="inlineStr">
         <is>
@@ -1140,7 +1136,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616</t>
+          <t xml:space="preserve">1503</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1165,38 +1161,38 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">155250</t>
+          <t xml:space="preserve">155166</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURNET RD E/S S/O HANCOCK DR.</t>
+          <t xml:space="preserve">I-35 @ MM 265.2 IN GEORGETOWN</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin</t>
+          <t xml:space="preserve">Georgetown</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78756</t>
+          <t xml:space="preserve">78628</t>
         </is>
       </c>
       <c r="K12" s="10">
-        <v>30.3232</v>
+        <v>30.683</v>
       </c>
       <c r="L12" s="10">
-        <v>-97.7392</v>
+        <v>-97.6604</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' 0" x 48' 0"</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1227,15 +1223,15 @@
         </is>
       </c>
       <c r="U12" s="4">
-        <v>82848</v>
+        <v>407496</v>
       </c>
       <c r="V12" s="8">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="W12" s="8"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="Z12" s="12" t="inlineStr">
         <is>
@@ -1250,7 +1246,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1622</t>
+          <t xml:space="preserve">1616</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1280,12 +1276,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">155256</t>
+          <t xml:space="preserve">155250</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35-E/S, 0.25 MI N/O HWY 183</t>
+          <t xml:space="preserve">BURNET RD E/S S/O HANCOCK DR.</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -1295,14 +1291,14 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78753</t>
+          <t xml:space="preserve">78756</t>
         </is>
       </c>
       <c r="K13" s="11">
-        <v>30.34809</v>
+        <v>30.3232</v>
       </c>
       <c r="L13" s="11">
-        <v>-97.693785</v>
+        <v>-97.7392</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
@@ -1337,15 +1333,15 @@
         </is>
       </c>
       <c r="U13" s="5">
-        <v>647970</v>
+        <v>82848</v>
       </c>
       <c r="V13" s="9">
-        <v>5400</v>
+        <v>3600</v>
       </c>
       <c r="W13" s="9"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="5">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="Z13" s="13" t="inlineStr">
         <is>
@@ -1360,7 +1356,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1627</t>
+          <t xml:space="preserve">1622</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1385,34 +1381,34 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">155259</t>
+          <t xml:space="preserve">155256</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S IH-35 @ INNER SPACE</t>
+          <t xml:space="preserve">IH-35-E/S, 0.25 MI N/O HWY 183</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georgetown</t>
+          <t xml:space="preserve">Austin</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78628</t>
+          <t xml:space="preserve">78753</t>
         </is>
       </c>
       <c r="K14" s="10">
-        <v>30.6108</v>
+        <v>30.34809</v>
       </c>
       <c r="L14" s="10">
-        <v>-97.6877</v>
+        <v>-97.693785</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -1421,12 +1417,12 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">14' 0" x 48' 0"</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1447,15 +1443,15 @@
         </is>
       </c>
       <c r="U14" s="4">
-        <v>475190</v>
+        <v>647970</v>
       </c>
       <c r="V14" s="8">
-        <v>5850</v>
+        <v>5400</v>
       </c>
       <c r="W14" s="8"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" s="12" t="inlineStr">
         <is>
@@ -1470,7 +1466,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25151</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1500,33 +1496,33 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">155549</t>
+          <t xml:space="preserve">155259</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/S SH 29 1.35 MI W/O US 183</t>
+          <t xml:space="preserve">W/S IH-35 @ INNER SPACE</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liberty Hill</t>
+          <t xml:space="preserve">Georgetown</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78642</t>
+          <t xml:space="preserve">78628</t>
         </is>
       </c>
       <c r="K15" s="11">
-        <v>30.6617</v>
+        <v>30.6108</v>
       </c>
       <c r="L15" s="11">
-        <v>-97.8974</v>
+        <v>-97.6877</v>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
@@ -1557,15 +1553,15 @@
         </is>
       </c>
       <c r="U15" s="5">
-        <v>166386</v>
+        <v>475190</v>
       </c>
       <c r="V15" s="9">
-        <v>2700</v>
+        <v>5850</v>
       </c>
       <c r="W15" s="9"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" s="13" t="inlineStr">
         <is>
@@ -1580,7 +1576,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">71011</t>
+          <t xml:space="preserve">25151</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1605,107 +1601,107 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30635644</t>
+          <t xml:space="preserve">155549</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S GUADALUPE @ NUECES</t>
-        </is>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+          <t xml:space="preserve">N/S SH 29 1.35 MI W/O US 183</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liberty Hill</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78642</t>
+        </is>
+      </c>
       <c r="K16" s="10">
-        <v>30.2945</v>
+        <v>30.6617</v>
       </c>
       <c r="L16" s="10">
-        <v>-97.7424</v>
+        <v>-97.8974</v>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' x 40'</t>
-        </is>
-      </c>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UT Guad HV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14' x 48'</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q16" s="4"/>
       <c r="R16" s="6">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="S16" s="6">
-        <v>46411</v>
+        <v>46327</v>
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.6.26 HEB 2026 Renewals (10491) C#5625829.pdf</t>
+          <t xml:space="preserve">Lamar C5659754 ATX 8-panel HEB-SIGNED 8-4-26 (awaiting Lamar GM).pdf</t>
         </is>
       </c>
       <c r="U16" s="4">
-        <v>107361</v>
+        <v>166386</v>
       </c>
       <c r="V16" s="8">
-        <v>10000</v>
+        <v>2700</v>
       </c>
       <c r="W16" s="8"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="Z16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
+      <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
       <c r="AC16" s="6"/>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCAA</t>
-        </is>
-      </c>
+      <c r="AD16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">01-011A-1</t>
+          <t xml:space="preserve">71011</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Media Choice</t>
+          <t xml:space="preserve">Lamar Advertising</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosie Miller</t>
+          <t xml:space="preserve">Brendolyn O'Connor</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">rmiller@mediachoice.com</t>
+          <t xml:space="preserve">boconnor@lamar.com</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1715,38 +1711,30 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30881052</t>
+          <t xml:space="preserve">30635644</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">13709 1/2 N, 250' N/O Howard Ln, Austin, TX, 78753</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Austin</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78753</t>
-        </is>
-      </c>
+          <t xml:space="preserve">W/S GUADALUPE @ NUECES</t>
+        </is>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="11">
-        <v>30.424998</v>
+        <v>30.2945</v>
       </c>
       <c r="L17" s="11">
-        <v>-97.670765</v>
+        <v>-97.7424</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
@@ -1756,66 +1744,74 @@
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q17" s="5"/>
+          <t xml:space="preserve">12' x 40'</t>
+        </is>
+      </c>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UT Guad HV</t>
+        </is>
+      </c>
       <c r="R17" s="7">
-        <v>46251</v>
+        <v>46209</v>
       </c>
       <c r="S17" s="7">
-        <v>46327</v>
+        <v>46411</v>
       </c>
       <c r="T17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Media Choice C209874 01-011A-1 HEB-SIGNED 8-4-26 (awaiting MC acceptance).pdf</t>
+          <t xml:space="preserve">7.6.26 HEB 2026 Renewals (10491) C#5625829.pdf</t>
         </is>
       </c>
       <c r="U17" s="5">
-        <v>910376</v>
+        <v>107361</v>
       </c>
       <c r="V17" s="9">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="W17" s="9"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA17" s="5"/>
+      <c r="AA17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
       <c r="AB17" s="5"/>
       <c r="AC17" s="7"/>
-      <c r="AD17" s="5"/>
+      <c r="AD17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCAA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX114A</t>
+          <t xml:space="preserve">01-011A-1</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MH Outdoor Media</t>
+          <t xml:space="preserve">Media Choice</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandon Wilburn</t>
+          <t xml:space="preserve">Rosie Miller</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bwilburn@machaik.com</t>
+          <t xml:space="preserve">rmiller@mediachoice.com</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1828,27 +1824,31 @@
           <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30881052</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S of IH-35, 250 feet S/o Old Bastrop Road.    San Marcos, TX, S/F</t>
+          <t xml:space="preserve">13709 1/2 N, 250' N/O Howard Ln, Austin, TX, 78753</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Braunfels</t>
+          <t xml:space="preserve">Austin</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78130</t>
+          <t xml:space="preserve">78753</t>
         </is>
       </c>
       <c r="K18" s="10">
-        <v>29.7814682</v>
+        <v>30.424998</v>
       </c>
       <c r="L18" s="10">
-        <v>-98.0324503</v>
+        <v>-97.670765</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -1872,26 +1872,26 @@
       </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="6">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="S18" s="6">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adkom_Contract_for_Signature_-_HEB.pdf</t>
+          <t xml:space="preserve">Media Choice C209874 01-011A-1 HEB-SIGNED 8-4-26 (awaiting MC acceptance).pdf</t>
         </is>
       </c>
       <c r="U18" s="4">
-        <v>1931923</v>
+        <v>910376</v>
       </c>
       <c r="V18" s="8">
-        <v>2818.66</v>
+        <v>5000</v>
       </c>
       <c r="W18" s="8"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" s="12" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX90B</t>
+          <t xml:space="preserve">TX114A</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1937,38 +1937,38 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S of FM 1325, 550 ft E/o CR 172, N/F</t>
+          <t xml:space="preserve">E/S of IH-35, 250 feet S/o Old Bastrop Road.    San Marcos, TX, S/F</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Austin</t>
+          <t xml:space="preserve">New Braunfels</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78728</t>
+          <t xml:space="preserve">78130</t>
         </is>
       </c>
       <c r="K19" s="11">
-        <v>30.47405</v>
+        <v>29.7814682</v>
       </c>
       <c r="L19" s="11">
-        <v>-97.688408</v>
+        <v>-98.0324503</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' x 40'</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P19" s="5" t="inlineStr">
@@ -1978,26 +1978,26 @@
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="S19" s="7">
-        <v>46327</v>
+        <v>46355</v>
       </c>
       <c r="T19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MH Outdoor 15447 TX90B HEB-SIGNED 8-4-26 (awaiting MH signature).pdf</t>
+          <t xml:space="preserve">Adkom_Contract_for_Signature_-_HEB.pdf</t>
         </is>
       </c>
       <c r="U19" s="5">
-        <v>353822</v>
+        <v>1931923</v>
       </c>
       <c r="V19" s="9">
-        <v>700</v>
+        <v>2818.66</v>
       </c>
       <c r="W19" s="9"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z19" s="13" t="inlineStr">
         <is>
@@ -2012,22 +2012,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">134</t>
+          <t xml:space="preserve">TX90B</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reagan Outdoor</t>
+          <t xml:space="preserve">MH Outdoor Media</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karen Goumakos</t>
+          <t xml:space="preserve">Brandon Wilburn</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">kgoumakos@reaganusa.com</t>
+          <t xml:space="preserve">bwilburn@machaik.com</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2040,14 +2040,10 @@
           <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">470717</t>
-        </is>
-      </c>
+      <c r="G20" s="4"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10720 I-35 N 0.3 mi S/O Braker Ln E WS</t>
+          <t xml:space="preserve">E/S of FM 1325, 550 ft E/o CR 172, N/F</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2057,14 +2053,14 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78753</t>
+          <t xml:space="preserve">78728</t>
         </is>
       </c>
       <c r="K20" s="10">
-        <v>30.373336</v>
+        <v>30.47405</v>
       </c>
       <c r="L20" s="10">
-        <v>-97.679089</v>
+        <v>-97.688408</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -2073,12 +2069,12 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' x 40'</t>
+          <t xml:space="preserve">12' x 40'</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
@@ -2091,23 +2087,23 @@
         <v>46251</v>
       </c>
       <c r="S20" s="6">
-        <v>46383</v>
+        <v>46327</v>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
+          <t xml:space="preserve">MH Outdoor 15447 TX90B HEB-SIGNED 8-4-26 (awaiting MH signature).pdf</t>
         </is>
       </c>
       <c r="U20" s="4">
-        <v>727696</v>
+        <v>353822</v>
       </c>
       <c r="V20" s="8">
-        <v>6350</v>
+        <v>700</v>
       </c>
       <c r="W20" s="8"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" s="12" t="inlineStr">
         <is>
@@ -2122,7 +2118,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">352</t>
+          <t xml:space="preserve">134</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2147,88 +2143,92 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">453921</t>
+          <t xml:space="preserve">470717</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">306 I-35 N 0.18 mi N/O 1st St E (Loop 343) WS</t>
-        </is>
-      </c>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+          <t xml:space="preserve">10720 I-35 N 0.3 mi S/O Braker Ln E WS</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austin</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78753</t>
+        </is>
+      </c>
       <c r="K21" s="11">
-        <v>30.26372</v>
+        <v>30.373336</v>
       </c>
       <c r="L21" s="11">
-        <v>-97.73606</v>
+        <v>-97.679089</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">North</t>
         </is>
       </c>
-      <c r="N21" s="5"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
-        </is>
-      </c>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I-35 DT HV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">10' x 40'</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q21" s="5"/>
       <c r="R21" s="7">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="S21" s="7">
-        <v>46355</v>
+        <v>46383</v>
       </c>
       <c r="T21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEB - B4670A (Direct).pdf</t>
+          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
         </is>
       </c>
       <c r="U21" s="5">
-        <v>1790665</v>
+        <v>727696</v>
       </c>
       <c r="V21" s="9">
-        <v>20735</v>
+        <v>6350</v>
       </c>
       <c r="W21" s="9"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
+      <c r="AA21" s="5"/>
       <c r="AB21" s="5"/>
       <c r="AC21" s="7"/>
-      <c r="AD21" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NCAA</t>
-        </is>
-      </c>
+      <c r="AD21" s="5"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">504</t>
+          <t xml:space="preserve">352</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2253,92 +2253,88 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">453965</t>
+          <t xml:space="preserve">453921</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11418 RR 2222 250 ft E/O FM 620 N NS</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Austin</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78730</t>
-        </is>
-      </c>
+          <t xml:space="preserve">306 I-35 N 0.18 mi N/O 1st St E (Loop 343) WS</t>
+        </is>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
       <c r="K22" s="10">
-        <v>30.40338</v>
+        <v>30.26372</v>
       </c>
       <c r="L22" s="10">
-        <v>-97.85314</v>
+        <v>-97.73606</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N22" s="4"/>
       <c r="O22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I-35 DT HV</t>
+        </is>
+      </c>
       <c r="R22" s="6">
-        <v>46251</v>
+        <v>46209</v>
       </c>
       <c r="S22" s="6">
-        <v>46313</v>
+        <v>46355</v>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
+          <t xml:space="preserve">HEB - B4670A (Direct).pdf</t>
         </is>
       </c>
       <c r="U22" s="4">
-        <v>341814</v>
+        <v>1790665</v>
       </c>
       <c r="V22" s="8">
-        <v>5830</v>
+        <v>20735</v>
       </c>
       <c r="W22" s="8"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA22" s="4"/>
+      <c r="AA22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
       <c r="AB22" s="4"/>
       <c r="AC22" s="6"/>
-      <c r="AD22" s="4"/>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NCAA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9041</t>
+          <t xml:space="preserve">504</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2368,12 +2364,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">454333</t>
+          <t xml:space="preserve">453965</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12200 Mo-Pac Expy N (Loop 1) 0.5 mi S/O Parmer Ln W (SR 734) WS</t>
+          <t xml:space="preserve">11418 RR 2222 250 ft E/O FM 620 N NS</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2383,23 +2379,23 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78758</t>
+          <t xml:space="preserve">78730</t>
         </is>
       </c>
       <c r="K23" s="11">
-        <v>30.41426</v>
+        <v>30.40338</v>
       </c>
       <c r="L23" s="11">
-        <v>-97.70797</v>
+        <v>-97.85314</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2414,10 +2410,10 @@
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="7">
-        <v>46293</v>
+        <v>46251</v>
       </c>
       <c r="S23" s="7">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
@@ -2425,15 +2421,15 @@
         </is>
       </c>
       <c r="U23" s="5">
-        <v>628643</v>
+        <v>341814</v>
       </c>
       <c r="V23" s="9">
-        <v>20350</v>
+        <v>5830</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Z23" s="13" t="inlineStr">
         <is>
@@ -2448,7 +2444,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9073</t>
+          <t xml:space="preserve">9041</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2478,12 +2474,12 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">454293</t>
+          <t xml:space="preserve">454333</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8304 US 290 E 0.3 mi W/O Springdale Rd NS</t>
+          <t xml:space="preserve">12200 Mo-Pac Expy N (Loop 1) 0.5 mi S/O Parmer Ln W (SR 734) WS</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2493,18 +2489,18 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78754</t>
+          <t xml:space="preserve">78758</t>
         </is>
       </c>
       <c r="K24" s="10">
-        <v>30.32867</v>
+        <v>30.41426</v>
       </c>
       <c r="L24" s="10">
-        <v>-97.66214</v>
+        <v>-97.70797</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2524,7 +2520,7 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="6">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="S24" s="6">
         <v>46327</v>
@@ -2535,15 +2531,15 @@
         </is>
       </c>
       <c r="U24" s="4">
-        <v>339031</v>
+        <v>628643</v>
       </c>
       <c r="V24" s="8">
-        <v>3860</v>
+        <v>20350</v>
       </c>
       <c r="W24" s="8"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="Z24" s="12" t="inlineStr">
         <is>
@@ -2558,7 +2554,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9078</t>
+          <t xml:space="preserve">9073</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2588,12 +2584,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">454358</t>
+          <t xml:space="preserve">454293</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">RR 2222 500 ft E/O RR 620 SS</t>
+          <t xml:space="preserve">8304 US 290 E 0.3 mi W/O Springdale Rd NS</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2603,14 +2599,14 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78730</t>
+          <t xml:space="preserve">78754</t>
         </is>
       </c>
       <c r="K25" s="11">
-        <v>30.40252</v>
+        <v>30.32867</v>
       </c>
       <c r="L25" s="11">
-        <v>-97.85297</v>
+        <v>-97.66214</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
@@ -2619,7 +2615,7 @@
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2634,7 +2630,7 @@
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="7">
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="S25" s="7">
         <v>46327</v>
@@ -2645,15 +2641,15 @@
         </is>
       </c>
       <c r="U25" s="5">
-        <v>125286</v>
+        <v>339031</v>
       </c>
       <c r="V25" s="9">
-        <v>3750</v>
+        <v>3860</v>
       </c>
       <c r="W25" s="9"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" s="13" t="inlineStr">
         <is>
@@ -2668,7 +2664,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345</t>
+          <t xml:space="preserve">9078</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2698,12 +2694,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14910666</t>
+          <t xml:space="preserve">454358</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10611 Research Blvd (US 183) 0.2 mi S/O Braker Ln W ES</t>
+          <t xml:space="preserve">RR 2222 500 ft E/O RR 620 SS</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2713,23 +2709,23 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78759</t>
+          <t xml:space="preserve">78730</t>
         </is>
       </c>
       <c r="K26" s="10">
-        <v>30.39775</v>
+        <v>30.40252</v>
       </c>
       <c r="L26" s="10">
-        <v>-97.74553</v>
+        <v>-97.85297</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
@@ -2755,10 +2751,10 @@
         </is>
       </c>
       <c r="U26" s="4">
-        <v>722818</v>
+        <v>125286</v>
       </c>
       <c r="V26" s="8">
-        <v>12925</v>
+        <v>3750</v>
       </c>
       <c r="W26" s="8"/>
       <c r="X26" s="4"/>
@@ -2778,7 +2774,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9507</t>
+          <t xml:space="preserve">9345</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2808,12 +2804,12 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30640678</t>
+          <t xml:space="preserve">14910666</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 I-35 S 500 ft N/O William Cannon WS</t>
+          <t xml:space="preserve">10611 Research Blvd (US 183) 0.2 mi S/O Braker Ln W ES</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2823,18 +2819,18 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78745</t>
+          <t xml:space="preserve">78759</t>
         </is>
       </c>
       <c r="K27" s="11">
-        <v>30.19184</v>
+        <v>30.39775</v>
       </c>
       <c r="L27" s="11">
-        <v>-97.77013</v>
+        <v>-97.74553</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
@@ -2854,10 +2850,10 @@
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="7">
-        <v>46293</v>
+        <v>46251</v>
       </c>
       <c r="S27" s="7">
-        <v>46376</v>
+        <v>46327</v>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
@@ -2865,15 +2861,15 @@
         </is>
       </c>
       <c r="U27" s="5">
-        <v>870619</v>
+        <v>722818</v>
       </c>
       <c r="V27" s="9">
-        <v>9295</v>
+        <v>12925</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="Z27" s="13" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9672</t>
+          <t xml:space="preserve">9507</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2918,12 +2914,12 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50753247</t>
+          <t xml:space="preserve">30640678</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 290 W 1370 ft W/O West Gate Blvd NS</t>
+          <t xml:space="preserve">6428 I-35 S 500 ft N/O William Cannon WS</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2933,18 +2929,18 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78735</t>
+          <t xml:space="preserve">78745</t>
         </is>
       </c>
       <c r="K28" s="10">
-        <v>30.232528</v>
+        <v>30.19184</v>
       </c>
       <c r="L28" s="10">
-        <v>-97.805155</v>
+        <v>-97.77013</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2964,10 +2960,10 @@
       </c>
       <c r="Q28" s="4"/>
       <c r="R28" s="6">
-        <v>46251</v>
+        <v>46293</v>
       </c>
       <c r="S28" s="6">
-        <v>46327</v>
+        <v>46376</v>
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
@@ -2975,15 +2971,15 @@
         </is>
       </c>
       <c r="U28" s="4">
-        <v>495015</v>
+        <v>870619</v>
       </c>
       <c r="V28" s="8">
-        <v>8450</v>
+        <v>9295</v>
       </c>
       <c r="W28" s="8"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="Z28" s="12" t="inlineStr">
         <is>
@@ -2998,18 +2994,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">189-3</t>
+          <t xml:space="preserve">9672</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Reiss Group</t>
-        </is>
-      </c>
-      <c r="C29" s="5"/>
+          <t xml:space="preserve">Reagan Outdoor</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Karen Goumakos</t>
+        </is>
+      </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisa@thereissgroup.net</t>
+          <t xml:space="preserve">kgoumakos@reaganusa.com</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3019,95 +3019,107 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
-        </is>
-      </c>
-      <c r="G29" s="5"/>
+          <t xml:space="preserve">Static Bulletin</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50753247</t>
+        </is>
+      </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35 near Hwy 123 (MP 203.7), 408 Patricia Dr, San Marcos, TX</t>
-        </is>
-      </c>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+          <t xml:space="preserve">Hwy 290 W 1370 ft W/O West Gate Blvd NS</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austin</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78735</t>
+        </is>
+      </c>
       <c r="K29" s="11">
-        <v>29.86349</v>
+        <v>30.232528</v>
       </c>
       <c r="L29" s="11">
-        <v>-97.94506</v>
-      </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
+        <v>-97.805155</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'' x 40''</t>
-        </is>
-      </c>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SM3 GO</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14' x 48'</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q29" s="5"/>
       <c r="R29" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="S29" s="7">
-        <v>46355</v>
+        <v>46327</v>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sam Marcos_GD.pdf</t>
+          <t xml:space="preserve">Reagan Q3Q4 2026 Bulletin HEB-signed (awaiting RNA President).pdf</t>
         </is>
       </c>
       <c r="U29" s="5">
-        <v>367525</v>
+        <v>495015</v>
       </c>
       <c r="V29" s="9">
-        <v>3090</v>
+        <v>8450</v>
       </c>
       <c r="W29" s="9"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO: Coming Soon</t>
-        </is>
-      </c>
+      <c r="AA29" s="5"/>
       <c r="AB29" s="5"/>
       <c r="AC29" s="7"/>
-      <c r="AD29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO: Date Reveal</t>
-        </is>
-      </c>
+      <c r="AD29" s="5"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">203-8051L</t>
+          <t xml:space="preserve">189-3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theon Properties</t>
+          <t xml:space="preserve">The Reiss Group</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
+          <t xml:space="preserve">Lisa</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+          <t xml:space="preserve">Lisa@thereissgroup.net</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3123,77 +3135,461 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35 NB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2"), 8360 I-35 frontage, Georgetown/Jarrell line</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jarrell</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78626</t>
-        </is>
-      </c>
+          <t xml:space="preserve">I-35 near Hwy 123 (MP 203.7), 408 Patricia Dr, San Marcos, TX</t>
+        </is>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="10">
-        <v>30.7645</v>
+        <v>29.86349</v>
       </c>
       <c r="L30" s="10">
-        <v>-97.6302</v>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+        <v>-97.94506</v>
+      </c>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14x48</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q30" s="4"/>
+          <t xml:space="preserve">12'' x 40''</t>
+        </is>
+      </c>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SM3 GO</t>
+        </is>
+      </c>
       <c r="R30" s="6">
-        <v>46296</v>
+        <v>46237</v>
       </c>
       <c r="S30" s="6">
-        <v>47026</v>
+        <v>46355</v>
       </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theon 8051L lease EXECUTED 8-4-26 (both signed).pdf</t>
+          <t xml:space="preserve">Sam Marcos_GD.pdf</t>
         </is>
       </c>
       <c r="U30" s="4">
-        <v>256803</v>
+        <v>367525</v>
       </c>
       <c r="V30" s="8">
-        <v>1000</v>
+        <v>3090</v>
       </c>
       <c r="W30" s="8"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA30" s="4"/>
+      <c r="AA30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Coming Soon</t>
+        </is>
+      </c>
       <c r="AB30" s="4"/>
       <c r="AC30" s="6"/>
-      <c r="AD30" s="4"/>
+      <c r="AD30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Date Reveal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203-8051L</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon Properties</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulletin</t>
+        </is>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IH-35 NB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2" south face), 8360 I-35 frontage, Georgetown/Jarrell line</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jarrell</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78626</t>
+        </is>
+      </c>
+      <c r="K31" s="11">
+        <v>30.7645</v>
+      </c>
+      <c r="L31" s="11">
+        <v>-97.6302</v>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">South</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14x48</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="7">
+        <v>46296</v>
+      </c>
+      <c r="S31" s="7">
+        <v>47026</v>
+      </c>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon 8051L lease EXECUTED 8-4-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U31" s="5">
+        <v>256803</v>
+      </c>
+      <c r="V31" s="9">
+        <v>1000</v>
+      </c>
+      <c r="W31" s="9"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5">
+        <v>9.9</v>
+      </c>
+      <c r="Z31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
+      <c r="AA31" s="5"/>
+      <c r="AB31" s="5"/>
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="5"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203-8051R</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon Properties</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mike Elliott (Elliott Properties Inc)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mike@elliottpropertiesinc.com</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bulletin</t>
+        </is>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IH-35 SB, 0.5 mi south of Ronald Reagan Blvd — SW corner IH-35 &amp; Ronald Reagan ("Sign No. 2" north face), 8360 I-35 frontage, Georgetown/Jarrell line</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jarrell</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78626</t>
+        </is>
+      </c>
+      <c r="K32" s="10">
+        <v>30.7645</v>
+      </c>
+      <c r="L32" s="10">
+        <v>-97.6302</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14x48</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="6">
+        <v>46357</v>
+      </c>
+      <c r="S32" s="6">
+        <v>47087</v>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theon 8051R lease EXECUTED 8-24-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U32" s="4">
+        <v>256803</v>
+      </c>
+      <c r="V32" s="8">
+        <v>1000</v>
+      </c>
+      <c r="W32" s="8"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="Z32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
+      <c r="AA32" s="4"/>
+      <c r="AB32" s="4"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="4"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TROOH.TXST.NOW</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trooh</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisa Nelson</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lisa@trooh.com</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place-Based - Digital Network ✨</t>
+        </is>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Texas State University, San Marcos (38,279 FTE) — all indoor high-traffic campus screens: rec centers, retail/bookstores, dining halls, student unions, student housing</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Marcos - Texas State campus</t>
+        </is>
+      </c>
+      <c r="J33" s="5"/>
+      <c r="K33" s="11">
+        <v>29.88962</v>
+      </c>
+      <c r="L33" s="11">
+        <v>-97.94462</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campus Digital Screens - Texas State University (San Marcos)</t>
+        </is>
+      </c>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trooh Media IO — H-E-B NOW Austin (UT Austin + Texas State campus digital screens), 9/4–10/31/26, $50,000 net — ✅ EXECUTED 9/3/26 (Nelson 9/3 + Sowrey 9/3)</t>
+        </is>
+      </c>
+      <c r="R33" s="7">
+        <v>46273</v>
+      </c>
+      <c r="S33" s="7">
+        <v>46326</v>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trooh IO HEB NOW Austin Sept-Oct26 v3 EXECUTED 9-3-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U33" s="5">
+        <v>208696</v>
+      </c>
+      <c r="V33" s="9">
+        <v>18000</v>
+      </c>
+      <c r="W33" s="9"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
+      <c r="AC33" s="7"/>
+      <c r="AD33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TROOH.UT.NOW</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trooh</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisa Nelson</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lisa@trooh.com</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Central</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place-Based - Digital Network ✨</t>
+        </is>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Texas at Austin (53,607 FTE) — all indoor high-traffic campus screens: rec centers, retail/bookstores, dining halls, student unions, student housing</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Austin - UT campus</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
+      <c r="K34" s="10">
+        <v>30.28732</v>
+      </c>
+      <c r="L34" s="10">
+        <v>-97.74239</v>
+      </c>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campus Digital Screens - University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trooh Media IO — H-E-B NOW Austin (UT Austin + Texas State campus digital screens), 9/4–10/31/26, $50,000 net — ✅ EXECUTED 9/3/26 (Nelson 9/3 + Sowrey 9/3)</t>
+        </is>
+      </c>
+      <c r="R34" s="6">
+        <v>46269</v>
+      </c>
+      <c r="S34" s="6">
+        <v>46326</v>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trooh IO HEB NOW Austin Sept-Oct26 v3 EXECUTED 9-3-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U34" s="4">
+        <v>371014</v>
+      </c>
+      <c r="V34" s="8">
+        <v>32000</v>
+      </c>
+      <c r="W34" s="8"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="Z34" s="4"/>
+      <c r="AA34" s="4"/>
+      <c r="AB34" s="4"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AD3"/>
@@ -3204,29 +3600,30 @@
   <hyperlinks>
     <hyperlink ref="Z4" r:id="rIdH1"/>
     <hyperlink ref="Z5" r:id="rIdH2"/>
-    <hyperlink ref="Z8" r:id="rIdH3"/>
-    <hyperlink ref="Z9" r:id="rIdH4"/>
-    <hyperlink ref="Z10" r:id="rIdH5"/>
-    <hyperlink ref="Z11" r:id="rIdH6"/>
-    <hyperlink ref="Z12" r:id="rIdH7"/>
-    <hyperlink ref="Z13" r:id="rIdH8"/>
-    <hyperlink ref="Z14" r:id="rIdH9"/>
-    <hyperlink ref="Z15" r:id="rIdH10"/>
-    <hyperlink ref="Z16" r:id="rIdH11"/>
-    <hyperlink ref="Z17" r:id="rIdH12"/>
-    <hyperlink ref="Z18" r:id="rIdH13"/>
-    <hyperlink ref="Z19" r:id="rIdH14"/>
-    <hyperlink ref="Z20" r:id="rIdH15"/>
-    <hyperlink ref="Z21" r:id="rIdH16"/>
-    <hyperlink ref="Z22" r:id="rIdH17"/>
-    <hyperlink ref="Z23" r:id="rIdH18"/>
-    <hyperlink ref="Z24" r:id="rIdH19"/>
-    <hyperlink ref="Z25" r:id="rIdH20"/>
-    <hyperlink ref="Z26" r:id="rIdH21"/>
-    <hyperlink ref="Z27" r:id="rIdH22"/>
-    <hyperlink ref="Z28" r:id="rIdH23"/>
-    <hyperlink ref="Z29" r:id="rIdH24"/>
-    <hyperlink ref="Z30" r:id="rIdH25"/>
+    <hyperlink ref="Z9" r:id="rIdH3"/>
+    <hyperlink ref="Z10" r:id="rIdH4"/>
+    <hyperlink ref="Z11" r:id="rIdH5"/>
+    <hyperlink ref="Z12" r:id="rIdH6"/>
+    <hyperlink ref="Z13" r:id="rIdH7"/>
+    <hyperlink ref="Z14" r:id="rIdH8"/>
+    <hyperlink ref="Z15" r:id="rIdH9"/>
+    <hyperlink ref="Z16" r:id="rIdH10"/>
+    <hyperlink ref="Z17" r:id="rIdH11"/>
+    <hyperlink ref="Z18" r:id="rIdH12"/>
+    <hyperlink ref="Z19" r:id="rIdH13"/>
+    <hyperlink ref="Z20" r:id="rIdH14"/>
+    <hyperlink ref="Z21" r:id="rIdH15"/>
+    <hyperlink ref="Z22" r:id="rIdH16"/>
+    <hyperlink ref="Z23" r:id="rIdH17"/>
+    <hyperlink ref="Z24" r:id="rIdH18"/>
+    <hyperlink ref="Z25" r:id="rIdH19"/>
+    <hyperlink ref="Z26" r:id="rIdH20"/>
+    <hyperlink ref="Z27" r:id="rIdH21"/>
+    <hyperlink ref="Z28" r:id="rIdH22"/>
+    <hyperlink ref="Z29" r:id="rIdH23"/>
+    <hyperlink ref="Z30" r:id="rIdH24"/>
+    <hyperlink ref="Z31" r:id="rIdH25"/>
+    <hyperlink ref="Z32" r:id="rIdH26"/>
   </hyperlinks>
 </worksheet>
 </file>